--- a/HCIT.xlsx
+++ b/HCIT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4074210C-800C-4D85-9D02-D2762ED6C8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0357DB3F-BE0F-46CF-8242-FD403B0C473E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{93B8E6DE-D491-4844-AF49-5C0F874FF622}"/>
+    <workbookView xWindow="4720" yWindow="5860" windowWidth="21120" windowHeight="12490" activeTab="1" xr2:uid="{93B8E6DE-D491-4844-AF49-5C0F874FF622}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="97">
   <si>
     <t>Main</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>TDOC</t>
+  </si>
+  <si>
+    <t>Fabric</t>
+  </si>
+  <si>
+    <t>https://www.fabrichealth.com/</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EF0DB2-30F2-49E4-BCD1-AAE960B87D9B}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1438,7 +1444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>56</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>58</v>
       </c>
@@ -1460,17 +1466,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>59</v>
       </c>
       <c r="G35" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{23AC5AD7-3BE0-455D-B1C9-03AAB7C9ABB1}"/>
+    <hyperlink ref="H37" r:id="rId1" xr:uid="{4FF1B8EC-D14A-4AB8-B3BE-3A72E2B4E7F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
